--- a/samples/out_test.xlsx
+++ b/samples/out_test.xlsx
@@ -785,7 +785,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7016,10 +7016,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BO3" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO3" s="65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -7222,10 +7220,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO4" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO4" s="65" t="n">
+        <v>0.4392</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -7428,10 +7424,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO5" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO5" s="65" t="n">
+        <v>0.2027</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -7634,10 +7628,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BO6" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO6" s="65" t="n">
+        <v>0.8784</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -7840,10 +7832,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO7" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO7" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -8046,10 +8036,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO8" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO8" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -8252,10 +8240,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO9" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO9" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -8458,10 +8444,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO10" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO10" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -8664,10 +8648,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO11" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO11" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -8870,10 +8852,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO12" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO12" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -9076,10 +9056,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO13" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO13" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -9282,10 +9260,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO14" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO14" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -9488,10 +9464,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO15" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO15" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -9694,10 +9668,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO16" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO16" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -9900,10 +9872,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO17" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO17" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
@@ -10106,10 +10076,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO18" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO18" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -10312,10 +10280,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO19" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO19" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -10518,10 +10484,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO20" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO20" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -10724,10 +10688,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO21" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO21" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -10930,10 +10892,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO22" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO22" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -11136,10 +11096,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO23" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO23" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -11342,10 +11300,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO24" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO24" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -11548,10 +11504,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO25" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO25" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -11754,10 +11708,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BO26" s="65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="BO26" s="65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27"/>
@@ -20404,18 +20356,6 @@
           <t>3h 1m 52s</t>
         </is>
       </c>
-      <c r="CR9" s="71" t="inlineStr">
-        <is>
-          <t>3. In-Meeting Activities</t>
-        </is>
-      </c>
-      <c r="CS9" s="71" t="inlineStr"/>
-      <c r="CT9" s="71" t="inlineStr"/>
-      <c r="CU9" s="72" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
@@ -20796,26 +20736,6 @@
       <c r="CP10" s="22" t="inlineStr">
         <is>
           <t>3h 1m 39s</t>
-        </is>
-      </c>
-      <c r="CR10" s="71" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="CS10" s="71" t="inlineStr">
-        <is>
-          <t>Join Time</t>
-        </is>
-      </c>
-      <c r="CT10" s="71" t="inlineStr">
-        <is>
-          <t>Leave Time</t>
-        </is>
-      </c>
-      <c r="CU10" s="72" t="inlineStr">
-        <is>
-          <t>0m</t>
         </is>
       </c>
     </row>
